--- a/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/CPL.xlsx
+++ b/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/CPL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="120" windowWidth="6855" windowHeight="6660"/>
+    <workbookView xWindow="240" yWindow="30" windowWidth="20055" windowHeight="7680"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <connection id="1" name="RADAR_Main_Board" type="6" refreshedVersion="3" background="1" saveData="1">
-    <textPr codePage="932" sourceFile="C:\Users\dell\Desktop\CrowdSupply\RADAR_V6\4_Schematics and Boards Layout\4_6_Schematics\MainBoard_Test\Gerber_Main_Board\RADAR_Main_Board.mnt" decimal="," thousands=" " space="1" consecutive="1">
+    <textPr codePage="932" sourceFile="C:\Users\dell\Desktop\CrowdSupply\RADAR_V6\4_Schematics and Boards Layout\4_7_Production Files\Gerber_Main_Board\RADAR_Main_Board.mnt" decimal="," thousands=" " space="1" consecutive="1">
       <textFields count="6">
         <textField/>
         <textField/>
@@ -5954,30 +5954,38 @@
     <t>208.60</t>
   </si>
   <si>
-    <t>DESIGNATOR</t>
-  </si>
-  <si>
-    <t>Mid_X(mm)</t>
-  </si>
-  <si>
-    <t>Mid_Y(mm)</t>
-  </si>
-  <si>
-    <t>LAYER</t>
-  </si>
-  <si>
-    <t>TOP</t>
-  </si>
-  <si>
-    <t>ROTATION</t>
+    <t>Layer</t>
+  </si>
+  <si>
+    <t>Designator</t>
+  </si>
+  <si>
+    <t>Mid X (mm)</t>
+  </si>
+  <si>
+    <t>Mid Y (mm)</t>
+  </si>
+  <si>
+    <t>Rotation</t>
+  </si>
+  <si>
+    <t>Top</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -6005,8 +6013,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6309,30 +6318,30 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="41" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="34.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1972</v>
       </c>
-      <c r="B1" t="s">
-        <v>1973</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1974</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1975</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1977</v>
+      <c r="E1" s="1" t="s">
+        <v>1976</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -6346,7 +6355,7 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E2">
         <v>180</v>
@@ -6363,7 +6372,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E3">
         <v>180</v>
@@ -6380,7 +6389,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -6397,7 +6406,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6414,7 +6423,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E6">
         <v>225</v>
@@ -6431,7 +6440,7 @@
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E7">
         <v>315</v>
@@ -6448,7 +6457,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E8">
         <v>135</v>
@@ -6465,7 +6474,7 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E9">
         <v>45</v>
@@ -6482,7 +6491,7 @@
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E10">
         <v>225</v>
@@ -6499,7 +6508,7 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E11">
         <v>315</v>
@@ -6516,7 +6525,7 @@
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E12">
         <v>135</v>
@@ -6533,7 +6542,7 @@
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E13">
         <v>45</v>
@@ -6550,7 +6559,7 @@
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E14">
         <v>225</v>
@@ -6567,7 +6576,7 @@
         <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E15">
         <v>315</v>
@@ -6584,7 +6593,7 @@
         <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E16">
         <v>135</v>
@@ -6601,7 +6610,7 @@
         <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E17">
         <v>45</v>
@@ -6618,7 +6627,7 @@
         <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E18">
         <v>225</v>
@@ -6635,7 +6644,7 @@
         <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E19">
         <v>315</v>
@@ -6652,7 +6661,7 @@
         <v>26</v>
       </c>
       <c r="D20" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E20">
         <v>135</v>
@@ -6669,7 +6678,7 @@
         <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E21">
         <v>45</v>
@@ -6686,7 +6695,7 @@
         <v>34</v>
       </c>
       <c r="D22" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -6703,7 +6712,7 @@
         <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6720,7 +6729,7 @@
         <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E24">
         <v>180</v>
@@ -6737,7 +6746,7 @@
         <v>42</v>
       </c>
       <c r="D25" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E25">
         <v>90</v>
@@ -6754,7 +6763,7 @@
         <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E26">
         <v>90</v>
@@ -6771,7 +6780,7 @@
         <v>45</v>
       </c>
       <c r="D27" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E27">
         <v>90</v>
@@ -6788,7 +6797,7 @@
         <v>45</v>
       </c>
       <c r="D28" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E28">
         <v>90</v>
@@ -6805,7 +6814,7 @@
         <v>52</v>
       </c>
       <c r="D29" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E29">
         <v>90</v>
@@ -6822,7 +6831,7 @@
         <v>52</v>
       </c>
       <c r="D30" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E30">
         <v>90</v>
@@ -6839,7 +6848,7 @@
         <v>52</v>
       </c>
       <c r="D31" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E31">
         <v>90</v>
@@ -6856,7 +6865,7 @@
         <v>52</v>
       </c>
       <c r="D32" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E32">
         <v>90</v>
@@ -6873,7 +6882,7 @@
         <v>52</v>
       </c>
       <c r="D33" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E33">
         <v>90</v>
@@ -6890,7 +6899,7 @@
         <v>63</v>
       </c>
       <c r="D34" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E34">
         <v>90</v>
@@ -6907,7 +6916,7 @@
         <v>66</v>
       </c>
       <c r="D35" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -6924,7 +6933,7 @@
         <v>69</v>
       </c>
       <c r="D36" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -6941,7 +6950,7 @@
         <v>72</v>
       </c>
       <c r="D37" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E37">
         <v>270</v>
@@ -6958,7 +6967,7 @@
         <v>75</v>
       </c>
       <c r="D38" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E38">
         <v>135</v>
@@ -6975,7 +6984,7 @@
         <v>78</v>
       </c>
       <c r="D39" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E39">
         <v>270</v>
@@ -6992,7 +7001,7 @@
         <v>81</v>
       </c>
       <c r="D40" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E40">
         <v>90</v>
@@ -7009,7 +7018,7 @@
         <v>84</v>
       </c>
       <c r="D41" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E41">
         <v>270</v>
@@ -7026,7 +7035,7 @@
         <v>87</v>
       </c>
       <c r="D42" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E42">
         <v>90</v>
@@ -7043,7 +7052,7 @@
         <v>90</v>
       </c>
       <c r="D43" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E43">
         <v>180</v>
@@ -7060,7 +7069,7 @@
         <v>93</v>
       </c>
       <c r="D44" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E44">
         <v>90</v>
@@ -7077,7 +7086,7 @@
         <v>96</v>
       </c>
       <c r="D45" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -7094,7 +7103,7 @@
         <v>99</v>
       </c>
       <c r="D46" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -7111,7 +7120,7 @@
         <v>102</v>
       </c>
       <c r="D47" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E47">
         <v>270</v>
@@ -7128,7 +7137,7 @@
         <v>105</v>
       </c>
       <c r="D48" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E48">
         <v>90</v>
@@ -7145,7 +7154,7 @@
         <v>108</v>
       </c>
       <c r="D49" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -7162,7 +7171,7 @@
         <v>108</v>
       </c>
       <c r="D50" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -7179,7 +7188,7 @@
         <v>113</v>
       </c>
       <c r="D51" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -7196,7 +7205,7 @@
         <v>116</v>
       </c>
       <c r="D52" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E52">
         <v>90</v>
@@ -7213,7 +7222,7 @@
         <v>119</v>
       </c>
       <c r="D53" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E53">
         <v>90</v>
@@ -7230,7 +7239,7 @@
         <v>122</v>
       </c>
       <c r="D54" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E54">
         <v>90</v>
@@ -7247,7 +7256,7 @@
         <v>124</v>
       </c>
       <c r="D55" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E55">
         <v>90</v>
@@ -7264,7 +7273,7 @@
         <v>127</v>
       </c>
       <c r="D56" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E56">
         <v>180</v>
@@ -7281,7 +7290,7 @@
         <v>130</v>
       </c>
       <c r="D57" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E57">
         <v>270</v>
@@ -7298,7 +7307,7 @@
         <v>133</v>
       </c>
       <c r="D58" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -7315,7 +7324,7 @@
         <v>136</v>
       </c>
       <c r="D59" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E59">
         <v>90</v>
@@ -7332,7 +7341,7 @@
         <v>139</v>
       </c>
       <c r="D60" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E60">
         <v>90</v>
@@ -7349,7 +7358,7 @@
         <v>142</v>
       </c>
       <c r="D61" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E61">
         <v>180</v>
@@ -7366,7 +7375,7 @@
         <v>145</v>
       </c>
       <c r="D62" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -7383,7 +7392,7 @@
         <v>147</v>
       </c>
       <c r="D63" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E63">
         <v>180</v>
@@ -7400,7 +7409,7 @@
         <v>149</v>
       </c>
       <c r="D64" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E64">
         <v>180</v>
@@ -7417,7 +7426,7 @@
         <v>152</v>
       </c>
       <c r="D65" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E65">
         <v>90</v>
@@ -7434,7 +7443,7 @@
         <v>155</v>
       </c>
       <c r="D66" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E66">
         <v>90</v>
@@ -7451,7 +7460,7 @@
         <v>158</v>
       </c>
       <c r="D67" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E67">
         <v>90</v>
@@ -7468,7 +7477,7 @@
         <v>161</v>
       </c>
       <c r="D68" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -7485,7 +7494,7 @@
         <v>164</v>
       </c>
       <c r="D69" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E69">
         <v>90</v>
@@ -7502,7 +7511,7 @@
         <v>167</v>
       </c>
       <c r="D70" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E70">
         <v>270</v>
@@ -7519,7 +7528,7 @@
         <v>170</v>
       </c>
       <c r="D71" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E71">
         <v>90</v>
@@ -7536,7 +7545,7 @@
         <v>173</v>
       </c>
       <c r="D72" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E72">
         <v>90</v>
@@ -7553,7 +7562,7 @@
         <v>176</v>
       </c>
       <c r="D73" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E73">
         <v>90</v>
@@ -7570,7 +7579,7 @@
         <v>179</v>
       </c>
       <c r="D74" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -7587,7 +7596,7 @@
         <v>182</v>
       </c>
       <c r="D75" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E75">
         <v>180</v>
@@ -7604,7 +7613,7 @@
         <v>185</v>
       </c>
       <c r="D76" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E76">
         <v>225</v>
@@ -7621,7 +7630,7 @@
         <v>188</v>
       </c>
       <c r="D77" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -7638,7 +7647,7 @@
         <v>191</v>
       </c>
       <c r="D78" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E78">
         <v>90</v>
@@ -7655,7 +7664,7 @@
         <v>194</v>
       </c>
       <c r="D79" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E79">
         <v>270</v>
@@ -7672,7 +7681,7 @@
         <v>197</v>
       </c>
       <c r="D80" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E80">
         <v>270</v>
@@ -7689,7 +7698,7 @@
         <v>200</v>
       </c>
       <c r="D81" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E81">
         <v>90</v>
@@ -7706,7 +7715,7 @@
         <v>203</v>
       </c>
       <c r="D82" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -7723,7 +7732,7 @@
         <v>206</v>
       </c>
       <c r="D83" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -7740,7 +7749,7 @@
         <v>209</v>
       </c>
       <c r="D84" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E84">
         <v>90</v>
@@ -7757,7 +7766,7 @@
         <v>212</v>
       </c>
       <c r="D85" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -7774,7 +7783,7 @@
         <v>206</v>
       </c>
       <c r="D86" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -7791,7 +7800,7 @@
         <v>217</v>
       </c>
       <c r="D87" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E87">
         <v>45</v>
@@ -7808,7 +7817,7 @@
         <v>220</v>
       </c>
       <c r="D88" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E88">
         <v>45</v>
@@ -7825,7 +7834,7 @@
         <v>223</v>
       </c>
       <c r="D89" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E89">
         <v>225</v>
@@ -7842,7 +7851,7 @@
         <v>226</v>
       </c>
       <c r="D90" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E90">
         <v>225</v>
@@ -7859,7 +7868,7 @@
         <v>229</v>
       </c>
       <c r="D91" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E91">
         <v>225</v>
@@ -7876,7 +7885,7 @@
         <v>232</v>
       </c>
       <c r="D92" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E92">
         <v>225</v>
@@ -7893,7 +7902,7 @@
         <v>235</v>
       </c>
       <c r="D93" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E93">
         <v>315</v>
@@ -7910,7 +7919,7 @@
         <v>238</v>
       </c>
       <c r="D94" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E94">
         <v>315</v>
@@ -7927,7 +7936,7 @@
         <v>241</v>
       </c>
       <c r="D95" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E95">
         <v>315</v>
@@ -7944,7 +7953,7 @@
         <v>244</v>
       </c>
       <c r="D96" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E96">
         <v>270</v>
@@ -7961,7 +7970,7 @@
         <v>247</v>
       </c>
       <c r="D97" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E97">
         <v>270</v>
@@ -7978,7 +7987,7 @@
         <v>250</v>
       </c>
       <c r="D98" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E98">
         <v>270</v>
@@ -7995,7 +8004,7 @@
         <v>253</v>
       </c>
       <c r="D99" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E99">
         <v>270</v>
@@ -8012,7 +8021,7 @@
         <v>256</v>
       </c>
       <c r="D100" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E100">
         <v>90</v>
@@ -8029,7 +8038,7 @@
         <v>256</v>
       </c>
       <c r="D101" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E101">
         <v>90</v>
@@ -8046,7 +8055,7 @@
         <v>261</v>
       </c>
       <c r="D102" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E102">
         <v>270</v>
@@ -8063,7 +8072,7 @@
         <v>261</v>
       </c>
       <c r="D103" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E103">
         <v>270</v>
@@ -8080,7 +8089,7 @@
         <v>266</v>
       </c>
       <c r="D104" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E104">
         <v>270</v>
@@ -8097,7 +8106,7 @@
         <v>269</v>
       </c>
       <c r="D105" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E105">
         <v>270</v>
@@ -8114,7 +8123,7 @@
         <v>272</v>
       </c>
       <c r="D106" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -8131,7 +8140,7 @@
         <v>275</v>
       </c>
       <c r="D107" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E107">
         <v>90</v>
@@ -8148,7 +8157,7 @@
         <v>278</v>
       </c>
       <c r="D108" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E108">
         <v>90</v>
@@ -8165,7 +8174,7 @@
         <v>278</v>
       </c>
       <c r="D109" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E109">
         <v>90</v>
@@ -8182,7 +8191,7 @@
         <v>283</v>
       </c>
       <c r="D110" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E110">
         <v>90</v>
@@ -8199,7 +8208,7 @@
         <v>286</v>
       </c>
       <c r="D111" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E111">
         <v>90</v>
@@ -8216,7 +8225,7 @@
         <v>289</v>
       </c>
       <c r="D112" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E112">
         <v>90</v>
@@ -8233,7 +8242,7 @@
         <v>292</v>
       </c>
       <c r="D113" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E113">
         <v>90</v>
@@ -8250,7 +8259,7 @@
         <v>292</v>
       </c>
       <c r="D114" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E114">
         <v>90</v>
@@ -8267,7 +8276,7 @@
         <v>297</v>
       </c>
       <c r="D115" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E115">
         <v>270</v>
@@ -8284,7 +8293,7 @@
         <v>300</v>
       </c>
       <c r="D116" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E116">
         <v>270</v>
@@ -8301,7 +8310,7 @@
         <v>303</v>
       </c>
       <c r="D117" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E117">
         <v>270</v>
@@ -8318,7 +8327,7 @@
         <v>303</v>
       </c>
       <c r="D118" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E118">
         <v>270</v>
@@ -8335,7 +8344,7 @@
         <v>308</v>
       </c>
       <c r="D119" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E119">
         <v>270</v>
@@ -8352,7 +8361,7 @@
         <v>311</v>
       </c>
       <c r="D120" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E120">
         <v>270</v>
@@ -8369,7 +8378,7 @@
         <v>314</v>
       </c>
       <c r="D121" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E121">
         <v>270</v>
@@ -8386,7 +8395,7 @@
         <v>314</v>
       </c>
       <c r="D122" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E122">
         <v>270</v>
@@ -8403,7 +8412,7 @@
         <v>319</v>
       </c>
       <c r="D123" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E123">
         <v>45</v>
@@ -8420,7 +8429,7 @@
         <v>322</v>
       </c>
       <c r="D124" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E124">
         <v>315</v>
@@ -8437,7 +8446,7 @@
         <v>325</v>
       </c>
       <c r="D125" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E125">
         <v>225</v>
@@ -8454,7 +8463,7 @@
         <v>328</v>
       </c>
       <c r="D126" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E126">
         <v>135</v>
@@ -8471,7 +8480,7 @@
         <v>331</v>
       </c>
       <c r="D127" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E127">
         <v>45</v>
@@ -8488,7 +8497,7 @@
         <v>334</v>
       </c>
       <c r="D128" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E128">
         <v>315</v>
@@ -8505,7 +8514,7 @@
         <v>337</v>
       </c>
       <c r="D129" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E129">
         <v>135</v>
@@ -8522,7 +8531,7 @@
         <v>340</v>
       </c>
       <c r="D130" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E130">
         <v>135</v>
@@ -8539,7 +8548,7 @@
         <v>343</v>
       </c>
       <c r="D131" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E131">
         <v>135</v>
@@ -8556,7 +8565,7 @@
         <v>346</v>
       </c>
       <c r="D132" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E132">
         <v>135</v>
@@ -8573,7 +8582,7 @@
         <v>348</v>
       </c>
       <c r="D133" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E133">
         <v>135</v>
@@ -8590,7 +8599,7 @@
         <v>351</v>
       </c>
       <c r="D134" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E134">
         <v>135</v>
@@ -8607,7 +8616,7 @@
         <v>328</v>
       </c>
       <c r="D135" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E135">
         <v>135</v>
@@ -8624,7 +8633,7 @@
         <v>356</v>
       </c>
       <c r="D136" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E136">
         <v>225</v>
@@ -8641,7 +8650,7 @@
         <v>359</v>
       </c>
       <c r="D137" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E137">
         <v>135</v>
@@ -8658,7 +8667,7 @@
         <v>362</v>
       </c>
       <c r="D138" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E138">
         <v>225</v>
@@ -8675,7 +8684,7 @@
         <v>365</v>
       </c>
       <c r="D139" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E139">
         <v>315</v>
@@ -8692,7 +8701,7 @@
         <v>368</v>
       </c>
       <c r="D140" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E140">
         <v>45</v>
@@ -8709,7 +8718,7 @@
         <v>371</v>
       </c>
       <c r="D141" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E141">
         <v>135</v>
@@ -8726,7 +8735,7 @@
         <v>374</v>
       </c>
       <c r="D142" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E142">
         <v>225</v>
@@ -8743,7 +8752,7 @@
         <v>377</v>
       </c>
       <c r="D143" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E143">
         <v>315</v>
@@ -8760,7 +8769,7 @@
         <v>380</v>
       </c>
       <c r="D144" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E144">
         <v>45</v>
@@ -8777,7 +8786,7 @@
         <v>383</v>
       </c>
       <c r="D145" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E145">
         <v>135</v>
@@ -8794,7 +8803,7 @@
         <v>386</v>
       </c>
       <c r="D146" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E146">
         <v>135</v>
@@ -8811,7 +8820,7 @@
         <v>389</v>
       </c>
       <c r="D147" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E147">
         <v>315</v>
@@ -8828,7 +8837,7 @@
         <v>392</v>
       </c>
       <c r="D148" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E148">
         <v>270</v>
@@ -8845,7 +8854,7 @@
         <v>395</v>
       </c>
       <c r="D149" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E149">
         <v>315</v>
@@ -8862,7 +8871,7 @@
         <v>398</v>
       </c>
       <c r="D150" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E150">
         <v>45</v>
@@ -8879,7 +8888,7 @@
         <v>401</v>
       </c>
       <c r="D151" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E151">
         <v>225</v>
@@ -8896,7 +8905,7 @@
         <v>404</v>
       </c>
       <c r="D152" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E152">
         <v>225</v>
@@ -8913,7 +8922,7 @@
         <v>407</v>
       </c>
       <c r="D153" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E153">
         <v>45</v>
@@ -8930,7 +8939,7 @@
         <v>410</v>
       </c>
       <c r="D154" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E154">
         <v>45</v>
@@ -8947,7 +8956,7 @@
         <v>413</v>
       </c>
       <c r="D155" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E155">
         <v>45</v>
@@ -8964,7 +8973,7 @@
         <v>416</v>
       </c>
       <c r="D156" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E156">
         <v>45</v>
@@ -8981,7 +8990,7 @@
         <v>419</v>
       </c>
       <c r="D157" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E157">
         <v>135</v>
@@ -8998,7 +9007,7 @@
         <v>422</v>
       </c>
       <c r="D158" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E158">
         <v>135</v>
@@ -9015,7 +9024,7 @@
         <v>425</v>
       </c>
       <c r="D159" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E159">
         <v>135</v>
@@ -9032,7 +9041,7 @@
         <v>428</v>
       </c>
       <c r="D160" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E160">
         <v>315</v>
@@ -9049,7 +9058,7 @@
         <v>431</v>
       </c>
       <c r="D161" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E161">
         <v>315</v>
@@ -9066,7 +9075,7 @@
         <v>392</v>
       </c>
       <c r="D162" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E162">
         <v>270</v>
@@ -9083,7 +9092,7 @@
         <v>436</v>
       </c>
       <c r="D163" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E163">
         <v>135</v>
@@ -9100,7 +9109,7 @@
         <v>439</v>
       </c>
       <c r="D164" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E164">
         <v>135</v>
@@ -9117,7 +9126,7 @@
         <v>442</v>
       </c>
       <c r="D165" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E165">
         <v>225</v>
@@ -9134,7 +9143,7 @@
         <v>445</v>
       </c>
       <c r="D166" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E166">
         <v>45</v>
@@ -9151,7 +9160,7 @@
         <v>448</v>
       </c>
       <c r="D167" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E167">
         <v>45</v>
@@ -9168,7 +9177,7 @@
         <v>451</v>
       </c>
       <c r="D168" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E168">
         <v>225</v>
@@ -9185,7 +9194,7 @@
         <v>454</v>
       </c>
       <c r="D169" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E169">
         <v>225</v>
@@ -9202,7 +9211,7 @@
         <v>457</v>
       </c>
       <c r="D170" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E170">
         <v>225</v>
@@ -9219,7 +9228,7 @@
         <v>460</v>
       </c>
       <c r="D171" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E171">
         <v>225</v>
@@ -9236,7 +9245,7 @@
         <v>463</v>
       </c>
       <c r="D172" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E172">
         <v>315</v>
@@ -9253,7 +9262,7 @@
         <v>466</v>
       </c>
       <c r="D173" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E173">
         <v>315</v>
@@ -9270,7 +9279,7 @@
         <v>469</v>
       </c>
       <c r="D174" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E174">
         <v>225</v>
@@ -9287,7 +9296,7 @@
         <v>472</v>
       </c>
       <c r="D175" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E175">
         <v>225</v>
@@ -9304,7 +9313,7 @@
         <v>475</v>
       </c>
       <c r="D176" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E176">
         <v>225</v>
@@ -9321,7 +9330,7 @@
         <v>478</v>
       </c>
       <c r="D177" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E177">
         <v>225</v>
@@ -9338,7 +9347,7 @@
         <v>481</v>
       </c>
       <c r="D178" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E178">
         <v>225</v>
@@ -9355,7 +9364,7 @@
         <v>484</v>
       </c>
       <c r="D179" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E179">
         <v>225</v>
@@ -9372,7 +9381,7 @@
         <v>487</v>
       </c>
       <c r="D180" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E180">
         <v>180</v>
@@ -9389,7 +9398,7 @@
         <v>490</v>
       </c>
       <c r="D181" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E181">
         <v>225</v>
@@ -9406,7 +9415,7 @@
         <v>493</v>
       </c>
       <c r="D182" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E182">
         <v>135</v>
@@ -9423,7 +9432,7 @@
         <v>496</v>
       </c>
       <c r="D183" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E183">
         <v>45</v>
@@ -9440,7 +9449,7 @@
         <v>499</v>
       </c>
       <c r="D184" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E184">
         <v>315</v>
@@ -9457,7 +9466,7 @@
         <v>502</v>
       </c>
       <c r="D185" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E185">
         <v>90</v>
@@ -9474,7 +9483,7 @@
         <v>505</v>
       </c>
       <c r="D186" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E186">
         <v>315</v>
@@ -9491,7 +9500,7 @@
         <v>508</v>
       </c>
       <c r="D187" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E187">
         <v>45</v>
@@ -9508,7 +9517,7 @@
         <v>511</v>
       </c>
       <c r="D188" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E188">
         <v>315</v>
@@ -9525,7 +9534,7 @@
         <v>514</v>
       </c>
       <c r="D189" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E189">
         <v>135</v>
@@ -9542,7 +9551,7 @@
         <v>517</v>
       </c>
       <c r="D190" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E190">
         <v>135</v>
@@ -9559,7 +9568,7 @@
         <v>519</v>
       </c>
       <c r="D191" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E191">
         <v>315</v>
@@ -9576,7 +9585,7 @@
         <v>522</v>
       </c>
       <c r="D192" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E192">
         <v>45</v>
@@ -9593,7 +9602,7 @@
         <v>525</v>
       </c>
       <c r="D193" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E193">
         <v>45</v>
@@ -9610,7 +9619,7 @@
         <v>528</v>
       </c>
       <c r="D194" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E194">
         <v>135</v>
@@ -9627,7 +9636,7 @@
         <v>531</v>
       </c>
       <c r="D195" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E195">
         <v>225</v>
@@ -9644,7 +9653,7 @@
         <v>534</v>
       </c>
       <c r="D196" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E196">
         <v>135</v>
@@ -9661,7 +9670,7 @@
         <v>537</v>
       </c>
       <c r="D197" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -9678,7 +9687,7 @@
         <v>539</v>
       </c>
       <c r="D198" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -9695,7 +9704,7 @@
         <v>541</v>
       </c>
       <c r="D199" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -9712,7 +9721,7 @@
         <v>544</v>
       </c>
       <c r="D200" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -9729,7 +9738,7 @@
         <v>547</v>
       </c>
       <c r="D201" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -9746,7 +9755,7 @@
         <v>549</v>
       </c>
       <c r="D202" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -9763,7 +9772,7 @@
         <v>552</v>
       </c>
       <c r="D203" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -9780,7 +9789,7 @@
         <v>555</v>
       </c>
       <c r="D204" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E204">
         <v>45</v>
@@ -9797,7 +9806,7 @@
         <v>558</v>
       </c>
       <c r="D205" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E205">
         <v>90</v>
@@ -9814,7 +9823,7 @@
         <v>561</v>
       </c>
       <c r="D206" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E206">
         <v>90</v>
@@ -9831,7 +9840,7 @@
         <v>564</v>
       </c>
       <c r="D207" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E207">
         <v>90</v>
@@ -9851,7 +9860,7 @@
         <v>568</v>
       </c>
       <c r="D208" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E208">
         <v>270</v>
@@ -9871,7 +9880,7 @@
         <v>571</v>
       </c>
       <c r="D209" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E209">
         <v>90</v>
@@ -9888,7 +9897,7 @@
         <v>574</v>
       </c>
       <c r="D210" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E210">
         <v>270</v>
@@ -9905,7 +9914,7 @@
         <v>577</v>
       </c>
       <c r="D211" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -9922,7 +9931,7 @@
         <v>580</v>
       </c>
       <c r="D212" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E212">
         <v>180</v>
@@ -9939,7 +9948,7 @@
         <v>583</v>
       </c>
       <c r="D213" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E213">
         <v>90</v>
@@ -9956,7 +9965,7 @@
         <v>586</v>
       </c>
       <c r="D214" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E214">
         <v>180</v>
@@ -9973,7 +9982,7 @@
         <v>589</v>
       </c>
       <c r="D215" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E215">
         <v>180</v>
@@ -9990,7 +9999,7 @@
         <v>592</v>
       </c>
       <c r="D216" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E216">
         <v>270</v>
@@ -10007,7 +10016,7 @@
         <v>595</v>
       </c>
       <c r="D217" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E217">
         <v>315</v>
@@ -10024,7 +10033,7 @@
         <v>598</v>
       </c>
       <c r="D218" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E218">
         <v>135</v>
@@ -10041,7 +10050,7 @@
         <v>383</v>
       </c>
       <c r="D219" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E219">
         <v>135</v>
@@ -10058,7 +10067,7 @@
         <v>603</v>
       </c>
       <c r="D220" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E220">
         <v>225</v>
@@ -10075,7 +10084,7 @@
         <v>606</v>
       </c>
       <c r="D221" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E221">
         <v>45</v>
@@ -10092,7 +10101,7 @@
         <v>609</v>
       </c>
       <c r="D222" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E222">
         <v>225</v>
@@ -10109,7 +10118,7 @@
         <v>612</v>
       </c>
       <c r="D223" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E223">
         <v>225</v>
@@ -10126,7 +10135,7 @@
         <v>615</v>
       </c>
       <c r="D224" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E224">
         <v>45</v>
@@ -10143,7 +10152,7 @@
         <v>618</v>
       </c>
       <c r="D225" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E225">
         <v>45</v>
@@ -10160,7 +10169,7 @@
         <v>621</v>
       </c>
       <c r="D226" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E226">
         <v>45</v>
@@ -10177,7 +10186,7 @@
         <v>623</v>
       </c>
       <c r="D227" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E227">
         <v>135</v>
@@ -10194,7 +10203,7 @@
         <v>626</v>
       </c>
       <c r="D228" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E228">
         <v>45</v>
@@ -10211,7 +10220,7 @@
         <v>629</v>
       </c>
       <c r="D229" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E229">
         <v>225</v>
@@ -10228,7 +10237,7 @@
         <v>632</v>
       </c>
       <c r="D230" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E230">
         <v>225</v>
@@ -10245,7 +10254,7 @@
         <v>635</v>
       </c>
       <c r="D231" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E231">
         <v>45</v>
@@ -10262,7 +10271,7 @@
         <v>638</v>
       </c>
       <c r="D232" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E232">
         <v>135</v>
@@ -10279,7 +10288,7 @@
         <v>641</v>
       </c>
       <c r="D233" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E233">
         <v>135</v>
@@ -10296,7 +10305,7 @@
         <v>644</v>
       </c>
       <c r="D234" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E234">
         <v>225</v>
@@ -10313,7 +10322,7 @@
         <v>647</v>
       </c>
       <c r="D235" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E235">
         <v>315</v>
@@ -10330,7 +10339,7 @@
         <v>650</v>
       </c>
       <c r="D236" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E236">
         <v>135</v>
@@ -10347,7 +10356,7 @@
         <v>653</v>
       </c>
       <c r="D237" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E237">
         <v>135</v>
@@ -10364,7 +10373,7 @@
         <v>656</v>
       </c>
       <c r="D238" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E238">
         <v>315</v>
@@ -10381,7 +10390,7 @@
         <v>659</v>
       </c>
       <c r="D239" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E239">
         <v>225</v>
@@ -10398,7 +10407,7 @@
         <v>662</v>
       </c>
       <c r="D240" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E240">
         <v>225</v>
@@ -10415,7 +10424,7 @@
         <v>665</v>
       </c>
       <c r="D241" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E241">
         <v>315</v>
@@ -10432,7 +10441,7 @@
         <v>668</v>
       </c>
       <c r="D242" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E242">
         <v>315</v>
@@ -10449,7 +10458,7 @@
         <v>671</v>
       </c>
       <c r="D243" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E243">
         <v>135</v>
@@ -10466,7 +10475,7 @@
         <v>674</v>
       </c>
       <c r="D244" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E244">
         <v>135</v>
@@ -10483,7 +10492,7 @@
         <v>677</v>
       </c>
       <c r="D245" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E245">
         <v>315</v>
@@ -10500,7 +10509,7 @@
         <v>680</v>
       </c>
       <c r="D246" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E246">
         <v>315</v>
@@ -10517,7 +10526,7 @@
         <v>683</v>
       </c>
       <c r="D247" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E247">
         <v>315</v>
@@ -10534,7 +10543,7 @@
         <v>686</v>
       </c>
       <c r="D248" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E248">
         <v>45</v>
@@ -10551,7 +10560,7 @@
         <v>689</v>
       </c>
       <c r="D249" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E249">
         <v>225</v>
@@ -10568,7 +10577,7 @@
         <v>692</v>
       </c>
       <c r="D250" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E250">
         <v>135</v>
@@ -10585,7 +10594,7 @@
         <v>695</v>
       </c>
       <c r="D251" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E251">
         <v>315</v>
@@ -10602,7 +10611,7 @@
         <v>698</v>
       </c>
       <c r="D252" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E252">
         <v>315</v>
@@ -10619,7 +10628,7 @@
         <v>701</v>
       </c>
       <c r="D253" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E253">
         <v>45</v>
@@ -10636,7 +10645,7 @@
         <v>704</v>
       </c>
       <c r="D254" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E254">
         <v>45</v>
@@ -10653,7 +10662,7 @@
         <v>707</v>
       </c>
       <c r="D255" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E255">
         <v>135</v>
@@ -10670,7 +10679,7 @@
         <v>710</v>
       </c>
       <c r="D256" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E256">
         <v>225</v>
@@ -10687,7 +10696,7 @@
         <v>713</v>
       </c>
       <c r="D257" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E257">
         <v>135</v>
@@ -10704,7 +10713,7 @@
         <v>716</v>
       </c>
       <c r="D258" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E258">
         <v>45</v>
@@ -10721,7 +10730,7 @@
         <v>719</v>
       </c>
       <c r="D259" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E259">
         <v>45</v>
@@ -10738,7 +10747,7 @@
         <v>722</v>
       </c>
       <c r="D260" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E260">
         <v>135</v>
@@ -10755,7 +10764,7 @@
         <v>725</v>
       </c>
       <c r="D261" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E261">
         <v>135</v>
@@ -10772,7 +10781,7 @@
         <v>728</v>
       </c>
       <c r="D262" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E262">
         <v>225</v>
@@ -10789,7 +10798,7 @@
         <v>730</v>
       </c>
       <c r="D263" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E263">
         <v>315</v>
@@ -10806,7 +10815,7 @@
         <v>733</v>
       </c>
       <c r="D264" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E264">
         <v>45</v>
@@ -10823,7 +10832,7 @@
         <v>736</v>
       </c>
       <c r="D265" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E265">
         <v>135</v>
@@ -10840,7 +10849,7 @@
         <v>739</v>
       </c>
       <c r="D266" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E266">
         <v>225</v>
@@ -10857,7 +10866,7 @@
         <v>742</v>
       </c>
       <c r="D267" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E267">
         <v>225</v>
@@ -10874,7 +10883,7 @@
         <v>745</v>
       </c>
       <c r="D268" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E268">
         <v>225</v>
@@ -10891,7 +10900,7 @@
         <v>748</v>
       </c>
       <c r="D269" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E269">
         <v>315</v>
@@ -10908,7 +10917,7 @@
         <v>751</v>
       </c>
       <c r="D270" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E270">
         <v>315</v>
@@ -10925,7 +10934,7 @@
         <v>754</v>
       </c>
       <c r="D271" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E271">
         <v>45</v>
@@ -10942,7 +10951,7 @@
         <v>757</v>
       </c>
       <c r="D272" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E272">
         <v>135</v>
@@ -10959,7 +10968,7 @@
         <v>760</v>
       </c>
       <c r="D273" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E273">
         <v>225</v>
@@ -10976,7 +10985,7 @@
         <v>763</v>
       </c>
       <c r="D274" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E274">
         <v>315</v>
@@ -10993,7 +11002,7 @@
         <v>766</v>
       </c>
       <c r="D275" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E275">
         <v>315</v>
@@ -11010,7 +11019,7 @@
         <v>769</v>
       </c>
       <c r="D276" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E276">
         <v>45</v>
@@ -11027,7 +11036,7 @@
         <v>772</v>
       </c>
       <c r="D277" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E277">
         <v>90</v>
@@ -11044,7 +11053,7 @@
         <v>775</v>
       </c>
       <c r="D278" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E278">
         <v>90</v>
@@ -11061,7 +11070,7 @@
         <v>778</v>
       </c>
       <c r="D279" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E279">
         <v>270</v>
@@ -11078,7 +11087,7 @@
         <v>781</v>
       </c>
       <c r="D280" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E280">
         <v>270</v>
@@ -11095,7 +11104,7 @@
         <v>784</v>
       </c>
       <c r="D281" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E281">
         <v>90</v>
@@ -11112,7 +11121,7 @@
         <v>787</v>
       </c>
       <c r="D282" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E282">
         <v>180</v>
@@ -11129,7 +11138,7 @@
         <v>790</v>
       </c>
       <c r="D283" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E283">
         <v>90</v>
@@ -11146,7 +11155,7 @@
         <v>793</v>
       </c>
       <c r="D284" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E284">
         <v>180</v>
@@ -11163,7 +11172,7 @@
         <v>796</v>
       </c>
       <c r="D285" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E285">
         <v>90</v>
@@ -11180,7 +11189,7 @@
         <v>799</v>
       </c>
       <c r="D286" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E286">
         <v>180</v>
@@ -11197,7 +11206,7 @@
         <v>802</v>
       </c>
       <c r="D287" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E287">
         <v>270</v>
@@ -11214,7 +11223,7 @@
         <v>805</v>
       </c>
       <c r="D288" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E288">
         <v>180</v>
@@ -11231,7 +11240,7 @@
         <v>808</v>
       </c>
       <c r="D289" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -11248,7 +11257,7 @@
         <v>811</v>
       </c>
       <c r="D290" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -11265,7 +11274,7 @@
         <v>814</v>
       </c>
       <c r="D291" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -11282,7 +11291,7 @@
         <v>817</v>
       </c>
       <c r="D292" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -11299,7 +11308,7 @@
         <v>820</v>
       </c>
       <c r="D293" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E293">
         <v>90</v>
@@ -11316,7 +11325,7 @@
         <v>823</v>
       </c>
       <c r="D294" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E294">
         <v>0</v>
@@ -11333,7 +11342,7 @@
         <v>826</v>
       </c>
       <c r="D295" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E295">
         <v>270</v>
@@ -11350,7 +11359,7 @@
         <v>823</v>
       </c>
       <c r="D296" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E296">
         <v>0</v>
@@ -11367,7 +11376,7 @@
         <v>831</v>
       </c>
       <c r="D297" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E297">
         <v>90</v>
@@ -11384,7 +11393,7 @@
         <v>834</v>
       </c>
       <c r="D298" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E298">
         <v>0</v>
@@ -11401,7 +11410,7 @@
         <v>836</v>
       </c>
       <c r="D299" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E299">
         <v>0</v>
@@ -11418,7 +11427,7 @@
         <v>839</v>
       </c>
       <c r="D300" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E300">
         <v>180</v>
@@ -11435,7 +11444,7 @@
         <v>842</v>
       </c>
       <c r="D301" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E301">
         <v>180</v>
@@ -11452,7 +11461,7 @@
         <v>845</v>
       </c>
       <c r="D302" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E302">
         <v>0</v>
@@ -11469,7 +11478,7 @@
         <v>799</v>
       </c>
       <c r="D303" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E303">
         <v>180</v>
@@ -11486,7 +11495,7 @@
         <v>850</v>
       </c>
       <c r="D304" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E304">
         <v>0</v>
@@ -11503,7 +11512,7 @@
         <v>787</v>
       </c>
       <c r="D305" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E305">
         <v>180</v>
@@ -11520,7 +11529,7 @@
         <v>855</v>
       </c>
       <c r="D306" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E306">
         <v>0</v>
@@ -11537,7 +11546,7 @@
         <v>787</v>
       </c>
       <c r="D307" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E307">
         <v>180</v>
@@ -11554,7 +11563,7 @@
         <v>859</v>
       </c>
       <c r="D308" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E308">
         <v>0</v>
@@ -11571,7 +11580,7 @@
         <v>823</v>
       </c>
       <c r="D309" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E309">
         <v>0</v>
@@ -11588,7 +11597,7 @@
         <v>863</v>
       </c>
       <c r="D310" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E310">
         <v>0</v>
@@ -11605,7 +11614,7 @@
         <v>866</v>
       </c>
       <c r="D311" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E311">
         <v>0</v>
@@ -11622,7 +11631,7 @@
         <v>868</v>
       </c>
       <c r="D312" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E312">
         <v>0</v>
@@ -11639,7 +11648,7 @@
         <v>817</v>
       </c>
       <c r="D313" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E313">
         <v>0</v>
@@ -11656,7 +11665,7 @@
         <v>872</v>
       </c>
       <c r="D314" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E314">
         <v>180</v>
@@ -11673,7 +11682,7 @@
         <v>823</v>
       </c>
       <c r="D315" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E315">
         <v>0</v>
@@ -11690,7 +11699,7 @@
         <v>877</v>
       </c>
       <c r="D316" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E316">
         <v>0</v>
@@ -11707,7 +11716,7 @@
         <v>880</v>
       </c>
       <c r="D317" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E317">
         <v>90</v>
@@ -11724,7 +11733,7 @@
         <v>882</v>
       </c>
       <c r="D318" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E318">
         <v>0</v>
@@ -11741,7 +11750,7 @@
         <v>885</v>
       </c>
       <c r="D319" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E319">
         <v>90</v>
@@ -11758,7 +11767,7 @@
         <v>888</v>
       </c>
       <c r="D320" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E320">
         <v>270</v>
@@ -11775,7 +11784,7 @@
         <v>890</v>
       </c>
       <c r="D321" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E321">
         <v>0</v>
@@ -11792,7 +11801,7 @@
         <v>888</v>
       </c>
       <c r="D322" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E322">
         <v>270</v>
@@ -11809,7 +11818,7 @@
         <v>895</v>
       </c>
       <c r="D323" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E323">
         <v>90</v>
@@ -11826,7 +11835,7 @@
         <v>885</v>
       </c>
       <c r="D324" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E324">
         <v>90</v>
@@ -11843,7 +11852,7 @@
         <v>900</v>
       </c>
       <c r="D325" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E325">
         <v>90</v>
@@ -11860,7 +11869,7 @@
         <v>903</v>
       </c>
       <c r="D326" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E326">
         <v>90</v>
@@ -11877,7 +11886,7 @@
         <v>906</v>
       </c>
       <c r="D327" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E327">
         <v>90</v>
@@ -11894,7 +11903,7 @@
         <v>900</v>
       </c>
       <c r="D328" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E328">
         <v>90</v>
@@ -11911,7 +11920,7 @@
         <v>911</v>
       </c>
       <c r="D329" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E329">
         <v>270</v>
@@ -11928,7 +11937,7 @@
         <v>914</v>
       </c>
       <c r="D330" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E330">
         <v>90</v>
@@ -11945,7 +11954,7 @@
         <v>917</v>
       </c>
       <c r="D331" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E331">
         <v>90</v>
@@ -11962,7 +11971,7 @@
         <v>920</v>
       </c>
       <c r="D332" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E332">
         <v>270</v>
@@ -11979,7 +11988,7 @@
         <v>923</v>
       </c>
       <c r="D333" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E333">
         <v>270</v>
@@ -11996,7 +12005,7 @@
         <v>926</v>
       </c>
       <c r="D334" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E334">
         <v>270</v>
@@ -12013,7 +12022,7 @@
         <v>926</v>
       </c>
       <c r="D335" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E335">
         <v>270</v>
@@ -12030,7 +12039,7 @@
         <v>931</v>
       </c>
       <c r="D336" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E336">
         <v>90</v>
@@ -12047,7 +12056,7 @@
         <v>934</v>
       </c>
       <c r="D337" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E337">
         <v>270</v>
@@ -12064,7 +12073,7 @@
         <v>937</v>
       </c>
       <c r="D338" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E338">
         <v>270</v>
@@ -12081,7 +12090,7 @@
         <v>940</v>
       </c>
       <c r="D339" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E339">
         <v>270</v>
@@ -12098,7 +12107,7 @@
         <v>943</v>
       </c>
       <c r="D340" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E340">
         <v>270</v>
@@ -12115,7 +12124,7 @@
         <v>946</v>
       </c>
       <c r="D341" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E341">
         <v>270</v>
@@ -12132,7 +12141,7 @@
         <v>949</v>
       </c>
       <c r="D342" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E342">
         <v>270</v>
@@ -12149,7 +12158,7 @@
         <v>952</v>
       </c>
       <c r="D343" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E343">
         <v>270</v>
@@ -12166,7 +12175,7 @@
         <v>955</v>
       </c>
       <c r="D344" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E344">
         <v>270</v>
@@ -12183,7 +12192,7 @@
         <v>958</v>
       </c>
       <c r="D345" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E345">
         <v>270</v>
@@ -12200,7 +12209,7 @@
         <v>960</v>
       </c>
       <c r="D346" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E346">
         <v>270</v>
@@ -12217,7 +12226,7 @@
         <v>963</v>
       </c>
       <c r="D347" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E347">
         <v>270</v>
@@ -12234,7 +12243,7 @@
         <v>966</v>
       </c>
       <c r="D348" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E348">
         <v>270</v>
@@ -12251,7 +12260,7 @@
         <v>969</v>
       </c>
       <c r="D349" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E349">
         <v>270</v>
@@ -12268,7 +12277,7 @@
         <v>972</v>
       </c>
       <c r="D350" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E350">
         <v>270</v>
@@ -12285,7 +12294,7 @@
         <v>302</v>
       </c>
       <c r="D351" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E351">
         <v>270</v>
@@ -12302,7 +12311,7 @@
         <v>977</v>
       </c>
       <c r="D352" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E352">
         <v>270</v>
@@ -12319,7 +12328,7 @@
         <v>977</v>
       </c>
       <c r="D353" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E353">
         <v>270</v>
@@ -12336,7 +12345,7 @@
         <v>982</v>
       </c>
       <c r="D354" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E354">
         <v>270</v>
@@ -12353,7 +12362,7 @@
         <v>985</v>
       </c>
       <c r="D355" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E355">
         <v>270</v>
@@ -12370,7 +12379,7 @@
         <v>988</v>
       </c>
       <c r="D356" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E356">
         <v>270</v>
@@ -12387,7 +12396,7 @@
         <v>991</v>
       </c>
       <c r="D357" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E357">
         <v>270</v>
@@ -12404,7 +12413,7 @@
         <v>994</v>
       </c>
       <c r="D358" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E358">
         <v>270</v>
@@ -12421,7 +12430,7 @@
         <v>996</v>
       </c>
       <c r="D359" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E359">
         <v>270</v>
@@ -12438,7 +12447,7 @@
         <v>999</v>
       </c>
       <c r="D360" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E360">
         <v>270</v>
@@ -12455,7 +12464,7 @@
         <v>1002</v>
       </c>
       <c r="D361" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E361">
         <v>180</v>
@@ -12472,7 +12481,7 @@
         <v>1005</v>
       </c>
       <c r="D362" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E362">
         <v>180</v>
@@ -12489,7 +12498,7 @@
         <v>1008</v>
       </c>
       <c r="D363" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E363">
         <v>270</v>
@@ -12506,7 +12515,7 @@
         <v>1011</v>
       </c>
       <c r="D364" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E364">
         <v>270</v>
@@ -12523,7 +12532,7 @@
         <v>1014</v>
       </c>
       <c r="D365" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E365">
         <v>90</v>
@@ -12540,7 +12549,7 @@
         <v>1017</v>
       </c>
       <c r="D366" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E366">
         <v>90</v>
@@ -12557,7 +12566,7 @@
         <v>1020</v>
       </c>
       <c r="D367" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E367">
         <v>270</v>
@@ -12574,7 +12583,7 @@
         <v>1023</v>
       </c>
       <c r="D368" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E368">
         <v>90</v>
@@ -12591,7 +12600,7 @@
         <v>1026</v>
       </c>
       <c r="D369" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E369">
         <v>90</v>
@@ -12608,7 +12617,7 @@
         <v>1029</v>
       </c>
       <c r="D370" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E370">
         <v>270</v>
@@ -12625,7 +12634,7 @@
         <v>778</v>
       </c>
       <c r="D371" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E371">
         <v>270</v>
@@ -12642,7 +12651,7 @@
         <v>1034</v>
       </c>
       <c r="D372" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E372">
         <v>90</v>
@@ -12659,7 +12668,7 @@
         <v>1037</v>
       </c>
       <c r="D373" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E373">
         <v>90</v>
@@ -12676,7 +12685,7 @@
         <v>1040</v>
       </c>
       <c r="D374" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E374">
         <v>90</v>
@@ -12693,7 +12702,7 @@
         <v>1043</v>
       </c>
       <c r="D375" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E375">
         <v>90</v>
@@ -12710,7 +12719,7 @@
         <v>1046</v>
       </c>
       <c r="D376" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E376">
         <v>90</v>
@@ -12727,7 +12736,7 @@
         <v>1049</v>
       </c>
       <c r="D377" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E377">
         <v>0</v>
@@ -12744,7 +12753,7 @@
         <v>1052</v>
       </c>
       <c r="D378" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E378">
         <v>0</v>
@@ -12761,7 +12770,7 @@
         <v>1055</v>
       </c>
       <c r="D379" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E379">
         <v>0</v>
@@ -12778,7 +12787,7 @@
         <v>1058</v>
       </c>
       <c r="D380" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E380">
         <v>0</v>
@@ -12795,7 +12804,7 @@
         <v>1061</v>
       </c>
       <c r="D381" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E381">
         <v>0</v>
@@ -12812,7 +12821,7 @@
         <v>1063</v>
       </c>
       <c r="D382" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E382">
         <v>0</v>
@@ -12829,7 +12838,7 @@
         <v>1066</v>
       </c>
       <c r="D383" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E383">
         <v>45</v>
@@ -12846,7 +12855,7 @@
         <v>1069</v>
       </c>
       <c r="D384" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E384">
         <v>45</v>
@@ -12863,7 +12872,7 @@
         <v>1072</v>
       </c>
       <c r="D385" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E385">
         <v>135</v>
@@ -12880,7 +12889,7 @@
         <v>1075</v>
       </c>
       <c r="D386" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E386">
         <v>225</v>
@@ -12897,7 +12906,7 @@
         <v>1078</v>
       </c>
       <c r="D387" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E387">
         <v>45</v>
@@ -12914,7 +12923,7 @@
         <v>1081</v>
       </c>
       <c r="D388" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E388">
         <v>45</v>
@@ -12931,7 +12940,7 @@
         <v>1084</v>
       </c>
       <c r="D389" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E389">
         <v>135</v>
@@ -12948,7 +12957,7 @@
         <v>1087</v>
       </c>
       <c r="D390" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E390">
         <v>45</v>
@@ -12965,7 +12974,7 @@
         <v>1090</v>
       </c>
       <c r="D391" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E391">
         <v>45</v>
@@ -12982,7 +12991,7 @@
         <v>1093</v>
       </c>
       <c r="D392" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E392">
         <v>45</v>
@@ -12999,7 +13008,7 @@
         <v>1096</v>
       </c>
       <c r="D393" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E393">
         <v>135</v>
@@ -13016,7 +13025,7 @@
         <v>1099</v>
       </c>
       <c r="D394" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E394">
         <v>45</v>
@@ -13033,7 +13042,7 @@
         <v>1102</v>
       </c>
       <c r="D395" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E395">
         <v>45</v>
@@ -13050,7 +13059,7 @@
         <v>1105</v>
       </c>
       <c r="D396" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E396">
         <v>45</v>
@@ -13067,7 +13076,7 @@
         <v>1108</v>
       </c>
       <c r="D397" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E397">
         <v>45</v>
@@ -13084,7 +13093,7 @@
         <v>1111</v>
       </c>
       <c r="D398" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E398">
         <v>45</v>
@@ -13101,7 +13110,7 @@
         <v>1114</v>
       </c>
       <c r="D399" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E399">
         <v>45</v>
@@ -13118,7 +13127,7 @@
         <v>1117</v>
       </c>
       <c r="D400" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E400">
         <v>45</v>
@@ -13135,7 +13144,7 @@
         <v>1120</v>
       </c>
       <c r="D401" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E401">
         <v>135</v>
@@ -13152,7 +13161,7 @@
         <v>1123</v>
       </c>
       <c r="D402" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E402">
         <v>45</v>
@@ -13169,7 +13178,7 @@
         <v>1126</v>
       </c>
       <c r="D403" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E403">
         <v>45</v>
@@ -13186,7 +13195,7 @@
         <v>1129</v>
       </c>
       <c r="D404" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E404">
         <v>45</v>
@@ -13203,7 +13212,7 @@
         <v>1132</v>
       </c>
       <c r="D405" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E405">
         <v>45</v>
@@ -13220,7 +13229,7 @@
         <v>1135</v>
       </c>
       <c r="D406" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E406">
         <v>45</v>
@@ -13237,7 +13246,7 @@
         <v>1138</v>
       </c>
       <c r="D407" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E407">
         <v>45</v>
@@ -13254,7 +13263,7 @@
         <v>1140</v>
       </c>
       <c r="D408" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E408">
         <v>45</v>
@@ -13271,7 +13280,7 @@
         <v>1143</v>
       </c>
       <c r="D409" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E409">
         <v>135</v>
@@ -13288,7 +13297,7 @@
         <v>1146</v>
       </c>
       <c r="D410" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E410">
         <v>45</v>
@@ -13305,7 +13314,7 @@
         <v>1149</v>
       </c>
       <c r="D411" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E411">
         <v>45</v>
@@ -13322,7 +13331,7 @@
         <v>1152</v>
       </c>
       <c r="D412" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E412">
         <v>45</v>
@@ -13339,7 +13348,7 @@
         <v>1155</v>
       </c>
       <c r="D413" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E413">
         <v>45</v>
@@ -13356,7 +13365,7 @@
         <v>1158</v>
       </c>
       <c r="D414" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E414">
         <v>45</v>
@@ -13373,7 +13382,7 @@
         <v>1161</v>
       </c>
       <c r="D415" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E415">
         <v>0</v>
@@ -13390,7 +13399,7 @@
         <v>1164</v>
       </c>
       <c r="D416" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E416">
         <v>270</v>
@@ -13407,7 +13416,7 @@
         <v>1167</v>
       </c>
       <c r="D417" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E417">
         <v>0</v>
@@ -13424,7 +13433,7 @@
         <v>206</v>
       </c>
       <c r="D418" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E418">
         <v>0</v>
@@ -13441,7 +13450,7 @@
         <v>1172</v>
       </c>
       <c r="D419" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E419">
         <v>0</v>
@@ -13458,7 +13467,7 @@
         <v>1175</v>
       </c>
       <c r="D420" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E420">
         <v>90</v>
@@ -13475,7 +13484,7 @@
         <v>1178</v>
       </c>
       <c r="D421" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E421">
         <v>90</v>
@@ -13492,7 +13501,7 @@
         <v>1181</v>
       </c>
       <c r="D422" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E422">
         <v>270</v>
@@ -13509,7 +13518,7 @@
         <v>212</v>
       </c>
       <c r="D423" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E423">
         <v>0</v>
@@ -13526,7 +13535,7 @@
         <v>1185</v>
       </c>
       <c r="D424" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E424">
         <v>0</v>
@@ -13543,7 +13552,7 @@
         <v>1188</v>
       </c>
       <c r="D425" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E425">
         <v>180</v>
@@ -13560,7 +13569,7 @@
         <v>1191</v>
       </c>
       <c r="D426" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E426">
         <v>0</v>
@@ -13577,7 +13586,7 @@
         <v>1194</v>
       </c>
       <c r="D427" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E427">
         <v>0</v>
@@ -13594,7 +13603,7 @@
         <v>1197</v>
       </c>
       <c r="D428" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E428">
         <v>180</v>
@@ -13611,7 +13620,7 @@
         <v>1200</v>
       </c>
       <c r="D429" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E429">
         <v>180</v>
@@ -13628,7 +13637,7 @@
         <v>427</v>
       </c>
       <c r="D430" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E430">
         <v>180</v>
@@ -13645,7 +13654,7 @@
         <v>990</v>
       </c>
       <c r="D431" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E431">
         <v>0</v>
@@ -13662,7 +13671,7 @@
         <v>1207</v>
       </c>
       <c r="D432" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E432">
         <v>0</v>
@@ -13679,7 +13688,7 @@
         <v>1210</v>
       </c>
       <c r="D433" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E433">
         <v>180</v>
@@ -13696,7 +13705,7 @@
         <v>1213</v>
       </c>
       <c r="D434" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E434">
         <v>180</v>
@@ -13713,7 +13722,7 @@
         <v>1216</v>
       </c>
       <c r="D435" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E435">
         <v>180</v>
@@ -13730,7 +13739,7 @@
         <v>1219</v>
       </c>
       <c r="D436" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E436">
         <v>0</v>
@@ -13747,7 +13756,7 @@
         <v>1222</v>
       </c>
       <c r="D437" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E437">
         <v>0</v>
@@ -13764,7 +13773,7 @@
         <v>1225</v>
       </c>
       <c r="D438" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E438">
         <v>0</v>
@@ -13781,7 +13790,7 @@
         <v>1228</v>
       </c>
       <c r="D439" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E439">
         <v>0</v>
@@ -13798,7 +13807,7 @@
         <v>1231</v>
       </c>
       <c r="D440" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E440">
         <v>0</v>
@@ -13815,7 +13824,7 @@
         <v>1234</v>
       </c>
       <c r="D441" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E441">
         <v>0</v>
@@ -13832,7 +13841,7 @@
         <v>814</v>
       </c>
       <c r="D442" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E442">
         <v>0</v>
@@ -13849,7 +13858,7 @@
         <v>1239</v>
       </c>
       <c r="D443" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E443">
         <v>90</v>
@@ -13866,7 +13875,7 @@
         <v>1242</v>
       </c>
       <c r="D444" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E444">
         <v>90</v>
@@ -13883,7 +13892,7 @@
         <v>1245</v>
       </c>
       <c r="D445" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E445">
         <v>90</v>
@@ -13900,7 +13909,7 @@
         <v>1057</v>
       </c>
       <c r="D446" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E446">
         <v>90</v>
@@ -13917,7 +13926,7 @@
         <v>1250</v>
       </c>
       <c r="D447" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E447">
         <v>270</v>
@@ -13934,7 +13943,7 @@
         <v>1253</v>
       </c>
       <c r="D448" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E448">
         <v>270</v>
@@ -13951,7 +13960,7 @@
         <v>1256</v>
       </c>
       <c r="D449" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E449">
         <v>180</v>
@@ -13968,7 +13977,7 @@
         <v>1259</v>
       </c>
       <c r="D450" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E450">
         <v>90</v>
@@ -13985,7 +13994,7 @@
         <v>544</v>
       </c>
       <c r="D451" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E451">
         <v>180</v>
@@ -14002,7 +14011,7 @@
         <v>1264</v>
       </c>
       <c r="D452" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E452">
         <v>180</v>
@@ -14019,7 +14028,7 @@
         <v>1267</v>
       </c>
       <c r="D453" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E453">
         <v>180</v>
@@ -14036,7 +14045,7 @@
         <v>1270</v>
       </c>
       <c r="D454" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E454">
         <v>180</v>
@@ -14053,7 +14062,7 @@
         <v>1273</v>
       </c>
       <c r="D455" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E455">
         <v>180</v>
@@ -14070,7 +14079,7 @@
         <v>1270</v>
       </c>
       <c r="D456" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E456">
         <v>180</v>
@@ -14087,7 +14096,7 @@
         <v>1278</v>
       </c>
       <c r="D457" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E457">
         <v>180</v>
@@ -14104,7 +14113,7 @@
         <v>1281</v>
       </c>
       <c r="D458" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E458">
         <v>270</v>
@@ -14121,7 +14130,7 @@
         <v>1284</v>
       </c>
       <c r="D459" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E459">
         <v>270</v>
@@ -14138,7 +14147,7 @@
         <v>1286</v>
       </c>
       <c r="D460" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E460">
         <v>180</v>
@@ -14155,7 +14164,7 @@
         <v>1288</v>
       </c>
       <c r="D461" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E461">
         <v>180</v>
@@ -14172,7 +14181,7 @@
         <v>1291</v>
       </c>
       <c r="D462" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E462">
         <v>180</v>
@@ -14189,7 +14198,7 @@
         <v>1294</v>
       </c>
       <c r="D463" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E463">
         <v>180</v>
@@ -14206,7 +14215,7 @@
         <v>1297</v>
       </c>
       <c r="D464" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E464">
         <v>0</v>
@@ -14223,7 +14232,7 @@
         <v>1300</v>
       </c>
       <c r="D465" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E465">
         <v>0</v>
@@ -14240,7 +14249,7 @@
         <v>1303</v>
       </c>
       <c r="D466" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E466">
         <v>180</v>
@@ -14257,7 +14266,7 @@
         <v>1303</v>
       </c>
       <c r="D467" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E467">
         <v>180</v>
@@ -14274,7 +14283,7 @@
         <v>1308</v>
       </c>
       <c r="D468" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E468">
         <v>180</v>
@@ -14291,7 +14300,7 @@
         <v>1311</v>
       </c>
       <c r="D469" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E469">
         <v>90</v>
@@ -14308,7 +14317,7 @@
         <v>1314</v>
       </c>
       <c r="D470" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E470">
         <v>90</v>
@@ -14325,7 +14334,7 @@
         <v>1317</v>
       </c>
       <c r="D471" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E471">
         <v>90</v>
@@ -14342,7 +14351,7 @@
         <v>1320</v>
       </c>
       <c r="D472" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E472">
         <v>90</v>
@@ -14359,7 +14368,7 @@
         <v>1323</v>
       </c>
       <c r="D473" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E473">
         <v>90</v>
@@ -14376,7 +14385,7 @@
         <v>1326</v>
       </c>
       <c r="D474" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E474">
         <v>90</v>
@@ -14393,7 +14402,7 @@
         <v>1329</v>
       </c>
       <c r="D475" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E475">
         <v>90</v>
@@ -14410,7 +14419,7 @@
         <v>1332</v>
       </c>
       <c r="D476" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E476">
         <v>90</v>
@@ -14427,7 +14436,7 @@
         <v>1335</v>
       </c>
       <c r="D477" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E477">
         <v>0</v>
@@ -14444,7 +14453,7 @@
         <v>1337</v>
       </c>
       <c r="D478" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E478">
         <v>180</v>
@@ -14461,7 +14470,7 @@
         <v>1340</v>
       </c>
       <c r="D479" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E479">
         <v>90</v>
@@ -14478,7 +14487,7 @@
         <v>1343</v>
       </c>
       <c r="D480" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E480">
         <v>0</v>
@@ -14495,7 +14504,7 @@
         <v>1346</v>
       </c>
       <c r="D481" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E481">
         <v>0</v>
@@ -14512,7 +14521,7 @@
         <v>1349</v>
       </c>
       <c r="D482" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E482">
         <v>180</v>
@@ -14529,7 +14538,7 @@
         <v>1352</v>
       </c>
       <c r="D483" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E483">
         <v>0</v>
@@ -14546,7 +14555,7 @@
         <v>1355</v>
       </c>
       <c r="D484" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E484">
         <v>90</v>
@@ -14563,7 +14572,7 @@
         <v>1358</v>
       </c>
       <c r="D485" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E485">
         <v>270</v>
@@ -14580,7 +14589,7 @@
         <v>1361</v>
       </c>
       <c r="D486" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E486">
         <v>270</v>
@@ -14597,7 +14606,7 @@
         <v>1364</v>
       </c>
       <c r="D487" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E487">
         <v>270</v>
@@ -14614,7 +14623,7 @@
         <v>1364</v>
       </c>
       <c r="D488" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E488">
         <v>270</v>
@@ -14631,7 +14640,7 @@
         <v>1369</v>
       </c>
       <c r="D489" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E489">
         <v>270</v>
@@ -14648,7 +14657,7 @@
         <v>1372</v>
       </c>
       <c r="D490" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E490">
         <v>270</v>
@@ -14665,7 +14674,7 @@
         <v>1375</v>
       </c>
       <c r="D491" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E491">
         <v>270</v>
@@ -14682,7 +14691,7 @@
         <v>291</v>
       </c>
       <c r="D492" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E492">
         <v>270</v>
@@ -14699,7 +14708,7 @@
         <v>1380</v>
       </c>
       <c r="D493" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E493">
         <v>270</v>
@@ -14716,7 +14725,7 @@
         <v>1383</v>
       </c>
       <c r="D494" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E494">
         <v>270</v>
@@ -14733,7 +14742,7 @@
         <v>1386</v>
       </c>
       <c r="D495" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E495">
         <v>180</v>
@@ -14750,7 +14759,7 @@
         <v>1389</v>
       </c>
       <c r="D496" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E496">
         <v>270</v>
@@ -14767,7 +14776,7 @@
         <v>1392</v>
       </c>
       <c r="D497" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E497">
         <v>0</v>
@@ -14784,7 +14793,7 @@
         <v>1395</v>
       </c>
       <c r="D498" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E498">
         <v>270</v>
@@ -14801,7 +14810,7 @@
         <v>1398</v>
       </c>
       <c r="D499" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E499">
         <v>270</v>
@@ -14818,7 +14827,7 @@
         <v>1401</v>
       </c>
       <c r="D500" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E500">
         <v>90</v>
@@ -14835,7 +14844,7 @@
         <v>1404</v>
       </c>
       <c r="D501" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E501">
         <v>90</v>
@@ -14852,7 +14861,7 @@
         <v>1407</v>
       </c>
       <c r="D502" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E502">
         <v>270</v>
@@ -14869,7 +14878,7 @@
         <v>297</v>
       </c>
       <c r="D503" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E503">
         <v>270</v>
@@ -14886,7 +14895,7 @@
         <v>311</v>
       </c>
       <c r="D504" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E504">
         <v>270</v>
@@ -14903,7 +14912,7 @@
         <v>1414</v>
       </c>
       <c r="D505" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E505">
         <v>270</v>
@@ -14920,7 +14929,7 @@
         <v>1417</v>
       </c>
       <c r="D506" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E506">
         <v>180</v>
@@ -14937,7 +14946,7 @@
         <v>1419</v>
       </c>
       <c r="D507" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E507">
         <v>0</v>
@@ -14954,7 +14963,7 @@
         <v>1422</v>
       </c>
       <c r="D508" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E508">
         <v>180</v>
@@ -14971,7 +14980,7 @@
         <v>1425</v>
       </c>
       <c r="D509" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E509">
         <v>180</v>
@@ -14988,7 +14997,7 @@
         <v>1428</v>
       </c>
       <c r="D510" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E510">
         <v>180</v>
@@ -15005,7 +15014,7 @@
         <v>1431</v>
       </c>
       <c r="D511" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E511">
         <v>270</v>
@@ -15022,7 +15031,7 @@
         <v>1434</v>
       </c>
       <c r="D512" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E512">
         <v>270</v>
@@ -15039,7 +15048,7 @@
         <v>1437</v>
       </c>
       <c r="D513" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E513">
         <v>270</v>
@@ -15056,7 +15065,7 @@
         <v>1440</v>
       </c>
       <c r="D514" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E514">
         <v>270</v>
@@ -15073,7 +15082,7 @@
         <v>1443</v>
       </c>
       <c r="D515" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E515">
         <v>0</v>
@@ -15090,7 +15099,7 @@
         <v>1446</v>
       </c>
       <c r="D516" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E516">
         <v>270</v>
@@ -15107,7 +15116,7 @@
         <v>1448</v>
       </c>
       <c r="D517" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E517">
         <v>270</v>
@@ -15124,7 +15133,7 @@
         <v>1451</v>
       </c>
       <c r="D518" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E518">
         <v>90</v>
@@ -15141,7 +15150,7 @@
         <v>1454</v>
       </c>
       <c r="D519" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E519">
         <v>90</v>
@@ -15158,7 +15167,7 @@
         <v>1457</v>
       </c>
       <c r="D520" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E520">
         <v>90</v>
@@ -15175,7 +15184,7 @@
         <v>1460</v>
       </c>
       <c r="D521" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E521">
         <v>90</v>
@@ -15192,7 +15201,7 @@
         <v>1463</v>
       </c>
       <c r="D522" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E522">
         <v>90</v>
@@ -15209,7 +15218,7 @@
         <v>1466</v>
       </c>
       <c r="D523" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E523">
         <v>90</v>
@@ -15226,7 +15235,7 @@
         <v>1446</v>
       </c>
       <c r="D524" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E524">
         <v>270</v>
@@ -15243,7 +15252,7 @@
         <v>1471</v>
       </c>
       <c r="D525" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E525">
         <v>90</v>
@@ -15260,7 +15269,7 @@
         <v>297</v>
       </c>
       <c r="D526" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E526">
         <v>90</v>
@@ -15277,7 +15286,7 @@
         <v>297</v>
       </c>
       <c r="D527" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E527">
         <v>90</v>
@@ -15294,7 +15303,7 @@
         <v>1478</v>
       </c>
       <c r="D528" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E528">
         <v>270</v>
@@ -15311,7 +15320,7 @@
         <v>1481</v>
       </c>
       <c r="D529" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E529">
         <v>0</v>
@@ -15328,7 +15337,7 @@
         <v>1484</v>
       </c>
       <c r="D530" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E530">
         <v>180</v>
@@ -15345,7 +15354,7 @@
         <v>1487</v>
       </c>
       <c r="D531" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E531">
         <v>270</v>
@@ -15362,7 +15371,7 @@
         <v>1490</v>
       </c>
       <c r="D532" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E532">
         <v>270</v>
@@ -15379,7 +15388,7 @@
         <v>47</v>
       </c>
       <c r="D533" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E533">
         <v>270</v>
@@ -15396,7 +15405,7 @@
         <v>1493</v>
       </c>
       <c r="D534" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E534">
         <v>270</v>
@@ -15413,7 +15422,7 @@
         <v>1496</v>
       </c>
       <c r="D535" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E535">
         <v>180</v>
@@ -15430,7 +15439,7 @@
         <v>1499</v>
       </c>
       <c r="D536" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E536">
         <v>0</v>
@@ -15447,7 +15456,7 @@
         <v>1342</v>
       </c>
       <c r="D537" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E537">
         <v>180</v>
@@ -15464,7 +15473,7 @@
         <v>1504</v>
       </c>
       <c r="D538" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E538">
         <v>0</v>
@@ -15481,7 +15490,7 @@
         <v>1506</v>
       </c>
       <c r="D539" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E539">
         <v>270</v>
@@ -15498,7 +15507,7 @@
         <v>1509</v>
       </c>
       <c r="D540" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E540">
         <v>270</v>
@@ -15515,7 +15524,7 @@
         <v>1512</v>
       </c>
       <c r="D541" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E541">
         <v>180</v>
@@ -15532,7 +15541,7 @@
         <v>1515</v>
       </c>
       <c r="D542" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E542">
         <v>0</v>
@@ -15549,7 +15558,7 @@
         <v>1342</v>
       </c>
       <c r="D543" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E543">
         <v>180</v>
@@ -15566,7 +15575,7 @@
         <v>1504</v>
       </c>
       <c r="D544" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E544">
         <v>0</v>
@@ -15583,7 +15592,7 @@
         <v>1522</v>
       </c>
       <c r="D545" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E545">
         <v>270</v>
@@ -15600,7 +15609,7 @@
         <v>1525</v>
       </c>
       <c r="D546" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E546">
         <v>270</v>
@@ -15617,7 +15626,7 @@
         <v>1527</v>
       </c>
       <c r="D547" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E547">
         <v>270</v>
@@ -15634,7 +15643,7 @@
         <v>1527</v>
       </c>
       <c r="D548" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E548">
         <v>270</v>
@@ -15651,7 +15660,7 @@
         <v>1532</v>
       </c>
       <c r="D549" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E549">
         <v>180</v>
@@ -15668,7 +15677,7 @@
         <v>1535</v>
       </c>
       <c r="D550" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E550">
         <v>0</v>
@@ -15685,7 +15694,7 @@
         <v>1537</v>
       </c>
       <c r="D551" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E551">
         <v>180</v>
@@ -15702,7 +15711,7 @@
         <v>1540</v>
       </c>
       <c r="D552" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E552">
         <v>0</v>
@@ -15719,7 +15728,7 @@
         <v>1543</v>
       </c>
       <c r="D553" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E553">
         <v>270</v>
@@ -15736,7 +15745,7 @@
         <v>1546</v>
       </c>
       <c r="D554" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E554">
         <v>270</v>
@@ -15753,7 +15762,7 @@
         <v>1548</v>
       </c>
       <c r="D555" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E555">
         <v>270</v>
@@ -15770,7 +15779,7 @@
         <v>1551</v>
       </c>
       <c r="D556" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E556">
         <v>270</v>
@@ -15787,7 +15796,7 @@
         <v>1553</v>
       </c>
       <c r="D557" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E557">
         <v>90</v>
@@ -15804,7 +15813,7 @@
         <v>268</v>
       </c>
       <c r="D558" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E558">
         <v>270</v>
@@ -15821,7 +15830,7 @@
         <v>268</v>
       </c>
       <c r="D559" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E559">
         <v>270</v>
@@ -15838,7 +15847,7 @@
         <v>268</v>
       </c>
       <c r="D560" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E560">
         <v>270</v>
@@ -15855,7 +15864,7 @@
         <v>1562</v>
       </c>
       <c r="D561" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E561">
         <v>90</v>
@@ -15872,7 +15881,7 @@
         <v>914</v>
       </c>
       <c r="D562" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E562">
         <v>270</v>
@@ -15889,7 +15898,7 @@
         <v>1567</v>
       </c>
       <c r="D563" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E563">
         <v>180</v>
@@ -15906,7 +15915,7 @@
         <v>1569</v>
       </c>
       <c r="D564" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E564">
         <v>270</v>
@@ -15923,7 +15932,7 @@
         <v>1572</v>
       </c>
       <c r="D565" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E565">
         <v>180</v>
@@ -15940,7 +15949,7 @@
         <v>1575</v>
       </c>
       <c r="D566" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E566">
         <v>0</v>
@@ -15957,7 +15966,7 @@
         <v>1391</v>
       </c>
       <c r="D567" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E567">
         <v>180</v>
@@ -15974,7 +15983,7 @@
         <v>1580</v>
       </c>
       <c r="D568" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E568">
         <v>0</v>
@@ -15991,7 +16000,7 @@
         <v>1583</v>
       </c>
       <c r="D569" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E569">
         <v>270</v>
@@ -16008,7 +16017,7 @@
         <v>1586</v>
       </c>
       <c r="D570" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E570">
         <v>90</v>
@@ -16025,7 +16034,7 @@
         <v>1589</v>
       </c>
       <c r="D571" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E571">
         <v>90</v>
@@ -16042,7 +16051,7 @@
         <v>1592</v>
       </c>
       <c r="D572" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E572">
         <v>90</v>
@@ -16059,7 +16068,7 @@
         <v>1595</v>
       </c>
       <c r="D573" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E573">
         <v>90</v>
@@ -16076,7 +16085,7 @@
         <v>1598</v>
       </c>
       <c r="D574" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E574">
         <v>270</v>
@@ -16093,7 +16102,7 @@
         <v>1601</v>
       </c>
       <c r="D575" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E575">
         <v>270</v>
@@ -16110,7 +16119,7 @@
         <v>1604</v>
       </c>
       <c r="D576" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E576">
         <v>270</v>
@@ -16127,7 +16136,7 @@
         <v>1607</v>
       </c>
       <c r="D577" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E577">
         <v>270</v>
@@ -16144,7 +16153,7 @@
         <v>1610</v>
       </c>
       <c r="D578" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E578">
         <v>180</v>
@@ -16161,7 +16170,7 @@
         <v>1586</v>
       </c>
       <c r="D579" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E579">
         <v>90</v>
@@ -16178,7 +16187,7 @@
         <v>1592</v>
       </c>
       <c r="D580" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E580">
         <v>90</v>
@@ -16195,7 +16204,7 @@
         <v>1595</v>
       </c>
       <c r="D581" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E581">
         <v>90</v>
@@ -16212,7 +16221,7 @@
         <v>1619</v>
       </c>
       <c r="D582" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E582">
         <v>90</v>
@@ -16229,7 +16238,7 @@
         <v>1607</v>
       </c>
       <c r="D583" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E583">
         <v>270</v>
@@ -16246,7 +16255,7 @@
         <v>1624</v>
       </c>
       <c r="D584" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E584">
         <v>180</v>
@@ -16263,7 +16272,7 @@
         <v>1626</v>
       </c>
       <c r="D585" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E585">
         <v>180</v>
@@ -16280,7 +16289,7 @@
         <v>1628</v>
       </c>
       <c r="D586" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E586">
         <v>180</v>
@@ -16297,7 +16306,7 @@
         <v>1630</v>
       </c>
       <c r="D587" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E587">
         <v>180</v>
@@ -16314,7 +16323,7 @@
         <v>1633</v>
       </c>
       <c r="D588" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E588">
         <v>0</v>
@@ -16331,7 +16340,7 @@
         <v>1635</v>
       </c>
       <c r="D589" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E589">
         <v>0</v>
@@ -16348,7 +16357,7 @@
         <v>1637</v>
       </c>
       <c r="D590" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E590">
         <v>0</v>
@@ -16365,7 +16374,7 @@
         <v>1640</v>
       </c>
       <c r="D591" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E591">
         <v>180</v>
@@ -16382,7 +16391,7 @@
         <v>1643</v>
       </c>
       <c r="D592" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E592">
         <v>270</v>
@@ -16399,7 +16408,7 @@
         <v>1604</v>
       </c>
       <c r="D593" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E593">
         <v>270</v>
@@ -16416,7 +16425,7 @@
         <v>1648</v>
       </c>
       <c r="D594" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E594">
         <v>270</v>
@@ -16433,7 +16442,7 @@
         <v>1604</v>
       </c>
       <c r="D595" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E595">
         <v>270</v>
@@ -16450,7 +16459,7 @@
         <v>1652</v>
       </c>
       <c r="D596" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E596">
         <v>180</v>
@@ -16467,7 +16476,7 @@
         <v>1655</v>
       </c>
       <c r="D597" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E597">
         <v>0</v>
@@ -16484,7 +16493,7 @@
         <v>1658</v>
       </c>
       <c r="D598" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E598">
         <v>90</v>
@@ -16501,7 +16510,7 @@
         <v>1661</v>
       </c>
       <c r="D599" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E599">
         <v>270</v>
@@ -16518,7 +16527,7 @@
         <v>1664</v>
       </c>
       <c r="D600" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E600">
         <v>0</v>
@@ -16535,7 +16544,7 @@
         <v>1664</v>
       </c>
       <c r="D601" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E601">
         <v>0</v>
@@ -16552,7 +16561,7 @@
         <v>1664</v>
       </c>
       <c r="D602" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E602">
         <v>0</v>
@@ -16569,7 +16578,7 @@
         <v>1664</v>
       </c>
       <c r="D603" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E603">
         <v>0</v>
@@ -16586,7 +16595,7 @@
         <v>1673</v>
       </c>
       <c r="D604" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E604">
         <v>0</v>
@@ -16603,7 +16612,7 @@
         <v>1675</v>
       </c>
       <c r="D605" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E605">
         <v>0</v>
@@ -16620,7 +16629,7 @@
         <v>1677</v>
       </c>
       <c r="D606" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E606">
         <v>0</v>
@@ -16637,7 +16646,7 @@
         <v>1679</v>
       </c>
       <c r="D607" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E607">
         <v>0</v>
@@ -16654,7 +16663,7 @@
         <v>1681</v>
       </c>
       <c r="D608" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E608">
         <v>0</v>
@@ -16671,7 +16680,7 @@
         <v>1683</v>
       </c>
       <c r="D609" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E609">
         <v>0</v>
@@ -16688,7 +16697,7 @@
         <v>1685</v>
       </c>
       <c r="D610" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E610">
         <v>0</v>
@@ -16705,7 +16714,7 @@
         <v>1688</v>
       </c>
       <c r="D611" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E611">
         <v>270</v>
@@ -16722,7 +16731,7 @@
         <v>1691</v>
       </c>
       <c r="D612" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E612">
         <v>270</v>
@@ -16739,7 +16748,7 @@
         <v>1694</v>
       </c>
       <c r="D613" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E613">
         <v>0</v>
@@ -16756,7 +16765,7 @@
         <v>1696</v>
       </c>
       <c r="D614" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E614">
         <v>0</v>
@@ -16773,7 +16782,7 @@
         <v>1699</v>
       </c>
       <c r="D615" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E615">
         <v>90</v>
@@ -16790,7 +16799,7 @@
         <v>1699</v>
       </c>
       <c r="D616" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E616">
         <v>90</v>
@@ -16807,7 +16816,7 @@
         <v>1704</v>
       </c>
       <c r="D617" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E617">
         <v>180</v>
@@ -16824,7 +16833,7 @@
         <v>1706</v>
       </c>
       <c r="D618" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E618">
         <v>180</v>
@@ -16841,7 +16850,7 @@
         <v>1709</v>
       </c>
       <c r="D619" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E619">
         <v>90</v>
@@ -16858,7 +16867,7 @@
         <v>1712</v>
       </c>
       <c r="D620" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E620">
         <v>315</v>
@@ -16875,7 +16884,7 @@
         <v>1714</v>
       </c>
       <c r="D621" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E621">
         <v>45</v>
@@ -16892,7 +16901,7 @@
         <v>1717</v>
       </c>
       <c r="D622" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E622">
         <v>225</v>
@@ -16909,7 +16918,7 @@
         <v>1720</v>
       </c>
       <c r="D623" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E623">
         <v>135</v>
@@ -16926,7 +16935,7 @@
         <v>1723</v>
       </c>
       <c r="D624" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E624">
         <v>315</v>
@@ -16943,7 +16952,7 @@
         <v>1089</v>
       </c>
       <c r="D625" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E625">
         <v>45</v>
@@ -16960,7 +16969,7 @@
         <v>1728</v>
       </c>
       <c r="D626" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E626">
         <v>225</v>
@@ -16977,7 +16986,7 @@
         <v>1731</v>
       </c>
       <c r="D627" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E627">
         <v>135</v>
@@ -16994,7 +17003,7 @@
         <v>1734</v>
       </c>
       <c r="D628" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E628">
         <v>315</v>
@@ -17011,7 +17020,7 @@
         <v>1737</v>
       </c>
       <c r="D629" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E629">
         <v>45</v>
@@ -17028,7 +17037,7 @@
         <v>1740</v>
       </c>
       <c r="D630" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E630">
         <v>225</v>
@@ -17045,7 +17054,7 @@
         <v>1743</v>
       </c>
       <c r="D631" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E631">
         <v>135</v>
@@ -17062,7 +17071,7 @@
         <v>1746</v>
       </c>
       <c r="D632" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E632">
         <v>315</v>
@@ -17079,7 +17088,7 @@
         <v>1749</v>
       </c>
       <c r="D633" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E633">
         <v>45</v>
@@ -17096,7 +17105,7 @@
         <v>1752</v>
       </c>
       <c r="D634" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E634">
         <v>225</v>
@@ -17113,7 +17122,7 @@
         <v>1755</v>
       </c>
       <c r="D635" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E635">
         <v>135</v>
@@ -17130,7 +17139,7 @@
         <v>1758</v>
       </c>
       <c r="D636" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E636">
         <v>90</v>
@@ -17147,7 +17156,7 @@
         <v>1761</v>
       </c>
       <c r="D637" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E637">
         <v>90</v>
@@ -17164,7 +17173,7 @@
         <v>1764</v>
       </c>
       <c r="D638" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E638">
         <v>270</v>
@@ -17181,7 +17190,7 @@
         <v>1767</v>
       </c>
       <c r="D639" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E639">
         <v>180</v>
@@ -17198,7 +17207,7 @@
         <v>1770</v>
       </c>
       <c r="D640" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E640">
         <v>0</v>
@@ -17215,7 +17224,7 @@
         <v>1772</v>
       </c>
       <c r="D641" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E641">
         <v>270</v>
@@ -17232,7 +17241,7 @@
         <v>1775</v>
       </c>
       <c r="D642" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E642">
         <v>180</v>
@@ -17249,7 +17258,7 @@
         <v>1210</v>
       </c>
       <c r="D643" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E643">
         <v>90</v>
@@ -17266,7 +17275,7 @@
         <v>1780</v>
       </c>
       <c r="D644" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E644">
         <v>90</v>
@@ -17283,7 +17292,7 @@
         <v>1783</v>
       </c>
       <c r="D645" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E645">
         <v>0</v>
@@ -17300,7 +17309,7 @@
         <v>1786</v>
       </c>
       <c r="D646" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E646">
         <v>0</v>
@@ -17317,7 +17326,7 @@
         <v>1789</v>
       </c>
       <c r="D647" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E647">
         <v>0</v>
@@ -17334,7 +17343,7 @@
         <v>1792</v>
       </c>
       <c r="D648" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E648">
         <v>90</v>
@@ -17351,7 +17360,7 @@
         <v>1795</v>
       </c>
       <c r="D649" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E649">
         <v>180</v>
@@ -17368,7 +17377,7 @@
         <v>1798</v>
       </c>
       <c r="D650" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E650">
         <v>0</v>
@@ -17385,7 +17394,7 @@
         <v>1801</v>
       </c>
       <c r="D651" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E651">
         <v>0</v>
@@ -17402,7 +17411,7 @@
         <v>1804</v>
       </c>
       <c r="D652" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E652">
         <v>180</v>
@@ -17419,7 +17428,7 @@
         <v>1807</v>
       </c>
       <c r="D653" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E653">
         <v>270</v>
@@ -17436,7 +17445,7 @@
         <v>1809</v>
       </c>
       <c r="D654" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E654">
         <v>270</v>
@@ -17453,7 +17462,7 @@
         <v>1812</v>
       </c>
       <c r="D655" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E655">
         <v>180</v>
@@ -17470,7 +17479,7 @@
         <v>1815</v>
       </c>
       <c r="D656" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E656">
         <v>225</v>
@@ -17487,7 +17496,7 @@
         <v>1818</v>
       </c>
       <c r="D657" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E657">
         <v>225</v>
@@ -17504,7 +17513,7 @@
         <v>1821</v>
       </c>
       <c r="D658" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E658">
         <v>135</v>
@@ -17521,7 +17530,7 @@
         <v>1824</v>
       </c>
       <c r="D659" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E659">
         <v>135</v>
@@ -17538,7 +17547,7 @@
         <v>1827</v>
       </c>
       <c r="D660" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E660">
         <v>45</v>
@@ -17555,7 +17564,7 @@
         <v>1830</v>
       </c>
       <c r="D661" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E661">
         <v>45</v>
@@ -17572,7 +17581,7 @@
         <v>1833</v>
       </c>
       <c r="D662" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E662">
         <v>0</v>
@@ -17589,7 +17598,7 @@
         <v>1836</v>
       </c>
       <c r="D663" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E663">
         <v>315</v>
@@ -17606,7 +17615,7 @@
         <v>1839</v>
       </c>
       <c r="D664" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E664">
         <v>315</v>
@@ -17623,7 +17632,7 @@
         <v>1842</v>
       </c>
       <c r="D665" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E665">
         <v>225</v>
@@ -17640,7 +17649,7 @@
         <v>1845</v>
       </c>
       <c r="D666" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E666">
         <v>225</v>
@@ -17657,7 +17666,7 @@
         <v>1848</v>
       </c>
       <c r="D667" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E667">
         <v>225</v>
@@ -17674,7 +17683,7 @@
         <v>1851</v>
       </c>
       <c r="D668" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E668">
         <v>225</v>
@@ -17691,7 +17700,7 @@
         <v>1854</v>
       </c>
       <c r="D669" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E669">
         <v>315</v>
@@ -17708,7 +17717,7 @@
         <v>1856</v>
       </c>
       <c r="D670" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E670">
         <v>315</v>
@@ -17725,7 +17734,7 @@
         <v>1859</v>
       </c>
       <c r="D671" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E671">
         <v>45</v>
@@ -17742,7 +17751,7 @@
         <v>1862</v>
       </c>
       <c r="D672" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E672">
         <v>45</v>
@@ -17759,7 +17768,7 @@
         <v>1865</v>
       </c>
       <c r="D673" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E673">
         <v>45</v>
@@ -17776,7 +17785,7 @@
         <v>1868</v>
       </c>
       <c r="D674" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E674">
         <v>45</v>
@@ -17793,7 +17802,7 @@
         <v>1871</v>
       </c>
       <c r="D675" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E675">
         <v>135</v>
@@ -17810,7 +17819,7 @@
         <v>1874</v>
       </c>
       <c r="D676" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E676">
         <v>135</v>
@@ -17827,7 +17836,7 @@
         <v>72</v>
       </c>
       <c r="D677" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E677">
         <v>225</v>
@@ -17844,7 +17853,7 @@
         <v>1878</v>
       </c>
       <c r="D678" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E678">
         <v>225</v>
@@ -17861,7 +17870,7 @@
         <v>1881</v>
       </c>
       <c r="D679" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E679">
         <v>315</v>
@@ -17878,7 +17887,7 @@
         <v>1884</v>
       </c>
       <c r="D680" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E680">
         <v>315</v>
@@ -17895,7 +17904,7 @@
         <v>1887</v>
       </c>
       <c r="D681" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E681">
         <v>315</v>
@@ -17912,7 +17921,7 @@
         <v>1890</v>
       </c>
       <c r="D682" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E682">
         <v>315</v>
@@ -17929,7 +17938,7 @@
         <v>1893</v>
       </c>
       <c r="D683" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E683">
         <v>45</v>
@@ -17946,7 +17955,7 @@
         <v>1896</v>
       </c>
       <c r="D684" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E684">
         <v>135</v>
@@ -17963,7 +17972,7 @@
         <v>1899</v>
       </c>
       <c r="D685" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E685">
         <v>135</v>
@@ -17980,7 +17989,7 @@
         <v>1902</v>
       </c>
       <c r="D686" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E686">
         <v>45</v>
@@ -17997,7 +18006,7 @@
         <v>1905</v>
       </c>
       <c r="D687" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E687">
         <v>135</v>
@@ -18014,7 +18023,7 @@
         <v>1908</v>
       </c>
       <c r="D688" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E688">
         <v>135</v>
@@ -18031,7 +18040,7 @@
         <v>1911</v>
       </c>
       <c r="D689" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E689">
         <v>0</v>
@@ -18048,7 +18057,7 @@
         <v>1014</v>
       </c>
       <c r="D690" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E690">
         <v>0</v>
@@ -18065,7 +18074,7 @@
         <v>1916</v>
       </c>
       <c r="D691" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E691">
         <v>0</v>
@@ -18082,7 +18091,7 @@
         <v>1919</v>
       </c>
       <c r="D692" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E692">
         <v>0</v>
@@ -18099,7 +18108,7 @@
         <v>1922</v>
       </c>
       <c r="D693" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E693">
         <v>180</v>
@@ -18116,7 +18125,7 @@
         <v>1925</v>
       </c>
       <c r="D694" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E694">
         <v>180</v>
@@ -18133,7 +18142,7 @@
         <v>1020</v>
       </c>
       <c r="D695" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E695">
         <v>180</v>
@@ -18150,7 +18159,7 @@
         <v>1930</v>
       </c>
       <c r="D696" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E696">
         <v>180</v>
@@ -18167,7 +18176,7 @@
         <v>1919</v>
       </c>
       <c r="D697" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E697">
         <v>0</v>
@@ -18184,7 +18193,7 @@
         <v>1023</v>
       </c>
       <c r="D698" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E698">
         <v>0</v>
@@ -18201,7 +18210,7 @@
         <v>1936</v>
       </c>
       <c r="D699" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E699">
         <v>0</v>
@@ -18218,7 +18227,7 @@
         <v>1939</v>
       </c>
       <c r="D700" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E700">
         <v>0</v>
@@ -18235,7 +18244,7 @@
         <v>1942</v>
       </c>
       <c r="D701" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E701">
         <v>180</v>
@@ -18252,7 +18261,7 @@
         <v>1945</v>
       </c>
       <c r="D702" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E702">
         <v>180</v>
@@ -18269,7 +18278,7 @@
         <v>1948</v>
       </c>
       <c r="D703" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E703">
         <v>180</v>
@@ -18286,7 +18295,7 @@
         <v>1951</v>
       </c>
       <c r="D704" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E704">
         <v>180</v>
@@ -18303,7 +18312,7 @@
         <v>1953</v>
       </c>
       <c r="D705" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E705">
         <v>0</v>
@@ -18320,7 +18329,7 @@
         <v>1956</v>
       </c>
       <c r="D706" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E706">
         <v>270</v>
@@ -18337,7 +18346,7 @@
         <v>1959</v>
       </c>
       <c r="D707" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E707">
         <v>0</v>
@@ -18354,7 +18363,7 @@
         <v>1962</v>
       </c>
       <c r="D708" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E708">
         <v>0</v>
@@ -18371,7 +18380,7 @@
         <v>1965</v>
       </c>
       <c r="D709" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E709">
         <v>270</v>
@@ -18388,7 +18397,7 @@
         <v>1968</v>
       </c>
       <c r="D710" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E710">
         <v>270</v>
@@ -18405,7 +18414,7 @@
         <v>1971</v>
       </c>
       <c r="D711" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E711">
         <v>60</v>
@@ -18413,6 +18422,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
